--- a/evaluation/train-test-splits/test_events.xlsx
+++ b/evaluation/train-test-splits/test_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,486 +435,392 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1434.519</v>
+        <v>2737.15</v>
       </c>
       <c r="B2" t="n">
-        <v>1435.086</v>
-      </c>
-      <c r="C2" t="n">
-        <v>412</v>
+        <v>2737.15</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1438.219</v>
+        <v>2764.45</v>
       </c>
       <c r="B3" t="n">
-        <v>1440.786</v>
-      </c>
-      <c r="C3" t="n">
-        <v>413</v>
+        <v>2766.75</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1440.819</v>
+        <v>2777.7</v>
       </c>
       <c r="B4" t="n">
-        <v>1441.352</v>
-      </c>
-      <c r="C4" t="n">
-        <v>412</v>
+        <v>2783.1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1443.419</v>
+        <v>2807.8</v>
       </c>
       <c r="B5" t="n">
-        <v>1443.986</v>
-      </c>
-      <c r="C5" t="n">
-        <v>405</v>
+        <v>2848.75</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1444.019</v>
+        <v>2861.5</v>
       </c>
       <c r="B6" t="n">
-        <v>1444.586</v>
-      </c>
-      <c r="C6" t="n">
-        <v>413</v>
+        <v>2863.25</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1444.719</v>
+        <v>2875.8</v>
       </c>
       <c r="B7" t="n">
-        <v>1445.586</v>
-      </c>
-      <c r="C7" t="n">
-        <v>405</v>
+        <v>2879.95</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1445.619</v>
+        <v>2880.95</v>
       </c>
       <c r="B8" t="n">
-        <v>1449.086</v>
-      </c>
-      <c r="C8" t="n">
-        <v>413</v>
+        <v>2883.9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1450.019</v>
+        <v>2894.55</v>
       </c>
       <c r="B9" t="n">
-        <v>1452.285</v>
-      </c>
-      <c r="C9" t="n">
-        <v>413</v>
+        <v>2896.1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1452.319</v>
+        <v>2963.05</v>
       </c>
       <c r="B10" t="n">
-        <v>1453.119</v>
-      </c>
-      <c r="C10" t="n">
-        <v>412</v>
+        <v>2966</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1462.919</v>
+        <v>2992.9</v>
       </c>
       <c r="B11" t="n">
-        <v>1463.552</v>
-      </c>
-      <c r="C11" t="n">
-        <v>405</v>
+        <v>2994.35</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1463.619</v>
+        <v>3016.85</v>
       </c>
       <c r="B12" t="n">
-        <v>1464.185</v>
-      </c>
-      <c r="C12" t="n">
-        <v>413</v>
+        <v>3021.7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1464.219</v>
+        <v>3053.25</v>
       </c>
       <c r="B13" t="n">
-        <v>1464.585</v>
-      </c>
-      <c r="C13" t="n">
-        <v>412</v>
+        <v>3069.95</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1465.585</v>
+        <v>3086.25</v>
       </c>
       <c r="B14" t="n">
-        <v>1468.352</v>
-      </c>
-      <c r="C14" t="n">
-        <v>413</v>
+        <v>3096.15</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1468.419</v>
+        <v>3108.85</v>
       </c>
       <c r="B15" t="n">
-        <v>1470.352</v>
-      </c>
-      <c r="C15" t="n">
-        <v>412</v>
+        <v>3113.25</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1471.419</v>
+        <v>3142.15</v>
       </c>
       <c r="B16" t="n">
-        <v>1471.952</v>
-      </c>
-      <c r="C16" t="n">
-        <v>405</v>
+        <v>3168.55</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1472.185</v>
+        <v>3177.85</v>
       </c>
       <c r="B17" t="n">
-        <v>1474.019</v>
-      </c>
-      <c r="C17" t="n">
-        <v>404</v>
+        <v>3179.2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1474.619</v>
+        <v>3192.45</v>
       </c>
       <c r="B18" t="n">
-        <v>1474.952</v>
-      </c>
-      <c r="C18" t="n">
-        <v>412</v>
+        <v>3194.4</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1480.219</v>
+        <v>3198.7</v>
       </c>
       <c r="B19" t="n">
-        <v>1480.685</v>
-      </c>
-      <c r="C19" t="n">
-        <v>405</v>
+        <v>3199.9</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1480.719</v>
+        <v>3202.85</v>
       </c>
       <c r="B20" t="n">
-        <v>1494.785</v>
-      </c>
-      <c r="C20" t="n">
-        <v>413</v>
+        <v>3205.2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1494.852</v>
+        <v>3220.95</v>
       </c>
       <c r="B21" t="n">
-        <v>1495.485</v>
-      </c>
-      <c r="C21" t="n">
-        <v>405</v>
+        <v>3222.15</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1495.552</v>
+        <v>3227.8</v>
       </c>
       <c r="B22" t="n">
-        <v>1496.285</v>
-      </c>
-      <c r="C22" t="n">
-        <v>406</v>
+        <v>3250.4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1496.318</v>
+        <v>3260.05</v>
       </c>
       <c r="B23" t="n">
-        <v>1497.252</v>
-      </c>
-      <c r="C23" t="n">
-        <v>404</v>
+        <v>3263.15</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1497.352</v>
+        <v>3270.2</v>
       </c>
       <c r="B24" t="n">
-        <v>1497.585</v>
-      </c>
-      <c r="C24" t="n">
-        <v>412</v>
+        <v>3270.4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1497.652</v>
+        <v>3333.15</v>
       </c>
       <c r="B25" t="n">
-        <v>1498.085</v>
-      </c>
-      <c r="C25" t="n">
-        <v>405</v>
+        <v>3338</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1498.252</v>
+        <v>3359.8</v>
       </c>
       <c r="B26" t="n">
-        <v>1499.185</v>
-      </c>
-      <c r="C26" t="n">
-        <v>406</v>
+        <v>3359.8</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1499.385</v>
+        <v>3377.5</v>
       </c>
       <c r="B27" t="n">
-        <v>1500.385</v>
-      </c>
-      <c r="C27" t="n">
-        <v>412</v>
+        <v>3381.15</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1509.118</v>
+        <v>3389.35</v>
       </c>
       <c r="B28" t="n">
-        <v>1510.218</v>
-      </c>
-      <c r="C28" t="n">
-        <v>405</v>
+        <v>3405.75</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1510.285</v>
+        <v>3424.5</v>
       </c>
       <c r="B29" t="n">
-        <v>1511.885</v>
-      </c>
-      <c r="C29" t="n">
-        <v>406</v>
+        <v>3545.45</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1513.785</v>
+        <v>3550.7</v>
       </c>
       <c r="B30" t="n">
-        <v>1513.985</v>
-      </c>
-      <c r="C30" t="n">
-        <v>412</v>
+        <v>3553.75</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1518.318</v>
+        <v>3556.7</v>
       </c>
       <c r="B31" t="n">
-        <v>1518.785</v>
-      </c>
-      <c r="C31" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1518.818</v>
-      </c>
-      <c r="B32" t="n">
-        <v>1520.985</v>
-      </c>
-      <c r="C32" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1521.051</v>
-      </c>
-      <c r="B33" t="n">
-        <v>1521.985</v>
-      </c>
-      <c r="C33" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1535.918</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1536.651</v>
-      </c>
-      <c r="C34" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1536.751</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1542.551</v>
-      </c>
-      <c r="C35" t="n">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1548.485</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1549.185</v>
-      </c>
-      <c r="C36" t="n">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1549.251</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1550.084</v>
-      </c>
-      <c r="C37" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1567.784</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1568.884</v>
-      </c>
-      <c r="C38" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1568.918</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1570.984</v>
-      </c>
-      <c r="C39" t="n">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1571.618</v>
-      </c>
-      <c r="B40" t="n">
-        <v>1572.118</v>
-      </c>
-      <c r="C40" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1574.618</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1575.384</v>
-      </c>
-      <c r="C41" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1575.451</v>
-      </c>
-      <c r="B42" t="n">
-        <v>1577.284</v>
-      </c>
-      <c r="C42" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1579.118</v>
-      </c>
-      <c r="B43" t="n">
-        <v>1579.884</v>
-      </c>
-      <c r="C43" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1583.717</v>
-      </c>
-      <c r="B44" t="n">
-        <v>1584.584</v>
-      </c>
-      <c r="C44" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1584.651</v>
-      </c>
-      <c r="B45" t="n">
-        <v>1588.951</v>
-      </c>
-      <c r="C45" t="n">
-        <v>404</v>
+        <v>3586.6</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
     </row>
   </sheetData>
